--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/on_yillik_maliyet.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/on_yillik_maliyet.xlsx
@@ -207,19 +207,19 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -642,17 +642,25 @@
           <t>PlanetDISK®</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>43586.32</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>379.2204</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>1219</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>35.6</v>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>44.742 €</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>379 €</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1.219 €</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>36 €</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -661,23 +669,31 @@
           <t>Aktif Çamur</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>32689.74</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>2425.644</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>4876</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>106.8</v>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>33.557 €</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>3.169 €</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>4.876 €</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>107 €</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>PlanetDISK® ile 10 Yıllık Toplam Kazanç: 60,000.00 ₺</t>
+          <t>PlanetDISK® DBD sistemin 10 yıl sonundaki toplam kazancı 70.000 EURO'dur</t>
         </is>
       </c>
       <c r="B5" s="14" t="n"/>
